--- a/data/trans_orig/P3A_R1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64006</t>
+          <t>66071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>458758</t>
+          <t>458347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479145</t>
+          <t>479317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430634</t>
+          <t>429256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449109</t>
+          <t>449118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>896685</t>
+          <t>894620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924685</t>
+          <t>924317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181991</t>
+          <t>183874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234248</t>
+          <t>234418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127346</t>
+          <t>129292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171349</t>
+          <t>171694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323531</t>
+          <t>325092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388273</t>
+          <t>390878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>501241</t>
+          <t>501071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>553498</t>
+          <t>551615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451470</t>
+          <t>451125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495473</t>
+          <t>493527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>970034</t>
+          <t>967429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1034776</t>
+          <t>1033215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169016</t>
+          <t>165536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213896</t>
+          <t>210408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85862</t>
+          <t>86476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124597</t>
+          <t>126361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>264864</t>
+          <t>265083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>323498</t>
+          <t>327220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423890</t>
+          <t>427378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468770</t>
+          <t>472250</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565147</t>
+          <t>563383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>603882</t>
+          <t>603268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004032</t>
+          <t>1000310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1062666</t>
+          <t>1062447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129408</t>
+          <t>130639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>125146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170020</t>
+          <t>170706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389739</t>
+          <t>388508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430184</t>
+          <t>428833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464991</t>
+          <t>465229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>488067</t>
+          <t>490450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>864769</t>
+          <t>864083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>912307</t>
+          <t>909643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67325</t>
+          <t>66545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44900</t>
+          <t>44664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68790</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103458</t>
+          <t>103303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319385</t>
+          <t>320165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348019</t>
+          <t>346520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>358071</t>
+          <t>358307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379655</t>
+          <t>379638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>686223</t>
+          <t>686378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>720891</t>
+          <t>722507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>55107</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84657</t>
+          <t>84230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30509</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51510</t>
+          <t>52699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>93196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131377</t>
+          <t>129946</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207926</t>
+          <t>208353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237489</t>
+          <t>237476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291424</t>
+          <t>290235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312425</t>
+          <t>312605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>504140</t>
+          <t>505571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542283</t>
+          <t>542321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24642</t>
+          <t>24785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>45190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62950</t>
+          <t>63320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164668</t>
+          <t>164693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>185241</t>
+          <t>185098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309376</t>
+          <t>309474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325093</t>
+          <t>324917</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480841</t>
+          <t>480471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>507189</t>
+          <t>507511</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>635310</t>
+          <t>640571</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>729493</t>
+          <t>736856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>367940</t>
+          <t>371045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>443267</t>
+          <t>445792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1031181</t>
+          <t>1029471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1145058</t>
+          <t>1154499</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2546168</t>
+          <t>2538805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2640351</t>
+          <t>2635090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2931378</t>
+          <t>2928853</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3006705</t>
+          <t>3003600</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5505249</t>
+          <t>5495808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5619126</t>
+          <t>5620836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46148</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>49379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80444</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412644</t>
+          <t>412186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434755</t>
+          <t>433619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384082</t>
+          <t>383938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405755</t>
+          <t>405590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803932</t>
+          <t>804674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834985</t>
+          <t>834997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171591</t>
+          <t>173550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218644</t>
+          <t>220864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143304</t>
+          <t>139703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188788</t>
+          <t>182845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325591</t>
+          <t>323846</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392951</t>
+          <t>390362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468443</t>
+          <t>466223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515496</t>
+          <t>513537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421467</t>
+          <t>427410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>466951</t>
+          <t>470552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>904391</t>
+          <t>906980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971751</t>
+          <t>973496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271523</t>
+          <t>271801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323122</t>
+          <t>321860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131349</t>
+          <t>130237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176538</t>
+          <t>175746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415519</t>
+          <t>415121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>486265</t>
+          <t>488272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>358741</t>
+          <t>360003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410340</t>
+          <t>410062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533310</t>
+          <t>534102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>578499</t>
+          <t>579611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>905446</t>
+          <t>903439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>976192</t>
+          <t>976590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182491</t>
+          <t>181598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232096</t>
+          <t>232826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60983</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96552</t>
+          <t>97154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254503</t>
+          <t>251905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>319124</t>
+          <t>313737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382521</t>
+          <t>381791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432126</t>
+          <t>433019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>519647</t>
+          <t>519045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>555216</t>
+          <t>554347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>911692</t>
+          <t>917079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>978911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>92861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133478</t>
+          <t>132274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37833</t>
+          <t>37210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67350</t>
+          <t>65860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140316</t>
+          <t>139894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187470</t>
+          <t>185440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294892</t>
+          <t>296096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>335509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>380450</t>
+          <t>381940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>409967</t>
+          <t>410590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688700</t>
+          <t>690730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>735854</t>
+          <t>736276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>84262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42714</t>
+          <t>42003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81217</t>
+          <t>82008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120866</t>
+          <t>118155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225068</t>
+          <t>225524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254892</t>
+          <t>255048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>310283</t>
+          <t>310994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>332979</t>
+          <t>332831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541917</t>
+          <t>544628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>581566</t>
+          <t>580775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45260</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39987</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69213</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204591</t>
+          <t>204254</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226401</t>
+          <t>227126</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>359079</t>
+          <t>358497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377572</t>
+          <t>376778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>569617</t>
+          <t>567691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598843</t>
+          <t>598472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>886882</t>
+          <t>885148</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>993468</t>
+          <t>996643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>482746</t>
+          <t>487569</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>572044</t>
+          <t>570891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1397854</t>
+          <t>1400238</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1539790</t>
+          <t>1548024</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2432251</t>
+          <t>2429076</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2538837</t>
+          <t>2540571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2984264</t>
+          <t>2985417</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3073562</t>
+          <t>3068739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5442237</t>
+          <t>5434003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5584173</t>
+          <t>5581789</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56364</t>
+          <t>57382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49030</t>
+          <t>50092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>81126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>386489</t>
+          <t>388004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404777</t>
+          <t>404400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339391</t>
+          <t>338373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>364345</t>
+          <t>364417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>733361</t>
+          <t>732257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764353</t>
+          <t>763291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195917</t>
+          <t>196601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243129</t>
+          <t>243568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127761</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167283</t>
+          <t>168887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339944</t>
+          <t>336065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402132</t>
+          <t>399993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347367</t>
+          <t>346928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394579</t>
+          <t>393895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395326</t>
+          <t>393722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>434848</t>
+          <t>434892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>750974</t>
+          <t>753113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>813162</t>
+          <t>817041</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286167</t>
+          <t>285381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338526</t>
+          <t>336624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195400</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241844</t>
+          <t>244327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496451</t>
+          <t>497066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>568560</t>
+          <t>566384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327869</t>
+          <t>329771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380228</t>
+          <t>381014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>418613</t>
+          <t>416130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465057</t>
+          <t>464381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>758292</t>
+          <t>760468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>830401</t>
+          <t>829786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220655</t>
+          <t>219486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268907</t>
+          <t>271523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106002</t>
+          <t>107307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147966</t>
+          <t>147825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340854</t>
+          <t>335982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>407038</t>
+          <t>404439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>374424</t>
+          <t>371808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>422676</t>
+          <t>423845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>500070</t>
+          <t>500211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>542034</t>
+          <t>540729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>884329</t>
+          <t>886928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>950513</t>
+          <t>955385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,98%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140175</t>
+          <t>139969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183159</t>
+          <t>184206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50823</t>
+          <t>50676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82468</t>
+          <t>83565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198932</t>
+          <t>199777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255075</t>
+          <t>252199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294759</t>
+          <t>293712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337743</t>
+          <t>337949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>413278</t>
+          <t>412181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444923</t>
+          <t>445070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>718589</t>
+          <t>721465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>774732</t>
+          <t>773887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76749</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109060</t>
+          <t>108619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52760</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110502</t>
+          <t>113058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151864</t>
+          <t>153560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224220</t>
+          <t>224661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256531</t>
+          <t>257305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>324048</t>
+          <t>326193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348097</t>
+          <t>349064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>558223</t>
+          <t>556527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599585</t>
+          <t>597029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>36609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80564</t>
+          <t>79404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198589</t>
+          <t>197180</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219774</t>
+          <t>219653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371611</t>
+          <t>371235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391725</t>
+          <t>391586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>575867</t>
+          <t>577027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>606539</t>
+          <t>607433</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1044449</t>
+          <t>1039782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1158096</t>
+          <t>1155736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>611538</t>
+          <t>610279</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>706442</t>
+          <t>703337</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1674992</t>
+          <t>1676119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1826342</t>
+          <t>1828966</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2227213</t>
+          <t>2229573</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2340860</t>
+          <t>2345527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2833138</t>
+          <t>2836243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2928042</t>
+          <t>2929301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5098548</t>
+          <t>5095924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5249898</t>
+          <t>5248771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41271</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74091</t>
+          <t>72548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353048</t>
+          <t>352493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386113</t>
+          <t>386925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271929</t>
+          <t>273594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297018</t>
+          <t>297523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>639096</t>
+          <t>640639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>680042</t>
+          <t>678644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99328</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150192</t>
+          <t>147199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72565</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139207</t>
+          <t>141984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180958</t>
+          <t>176405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275502</t>
+          <t>271058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273355</t>
+          <t>276348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324219</t>
+          <t>322333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372886</t>
+          <t>370109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439528</t>
+          <t>445100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>660138</t>
+          <t>664582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754682</t>
+          <t>759235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214377</t>
+          <t>211348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260781</t>
+          <t>260161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151557</t>
+          <t>154829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229525</t>
+          <t>230184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>378470</t>
+          <t>384427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>477593</t>
+          <t>478198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275557</t>
+          <t>276177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321961</t>
+          <t>324990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362477</t>
+          <t>361818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440445</t>
+          <t>437173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650747</t>
+          <t>650142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749870</t>
+          <t>743913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>93812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306541</t>
+          <t>308998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171657</t>
+          <t>171442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>223801</t>
+          <t>225337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>250884</t>
+          <t>256934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>507585</t>
+          <t>508589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581245</t>
+          <t>578788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>789922</t>
+          <t>793974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488386</t>
+          <t>486850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>540530</t>
+          <t>540745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1092388</t>
+          <t>1091384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1349089</t>
+          <t>1343039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156234</t>
+          <t>156183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197502</t>
+          <t>201514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100944</t>
+          <t>99637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128093</t>
+          <t>128405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263133</t>
+          <t>265628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315959</t>
+          <t>313863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363732</t>
+          <t>359720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>405000</t>
+          <t>405051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419812</t>
+          <t>419500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446961</t>
+          <t>448268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>793180</t>
+          <t>795276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>846006</t>
+          <t>843511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>87153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116072</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>83387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>75897</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201312</t>
+          <t>200516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250994</t>
+          <t>251986</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279272</t>
+          <t>279913</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>524327</t>
+          <t>524415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>585223</t>
+          <t>588511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>773557</t>
+          <t>774353</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>899828</t>
+          <t>898972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>46018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67320</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30760</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67764</t>
+          <t>67680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94364</t>
+          <t>92805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215439</t>
+          <t>215449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>237431</t>
+          <t>236741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>395071</t>
+          <t>395026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>407922</t>
+          <t>407809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614226</t>
+          <t>615785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640826</t>
+          <t>640910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>732759</t>
+          <t>734467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1022406</t>
+          <t>1027734</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>604305</t>
+          <t>592589</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>803283</t>
+          <t>809525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1453819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1794625</t>
+          <t>1803776</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2436312</t>
+          <t>2430984</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2725959</t>
+          <t>2724251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2907737</t>
+          <t>2901495</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3106715</t>
+          <t>3118431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5375113</t>
+          <t>5365962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5721138</t>
+          <t>5715919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>35411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37371</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36374</t>
+          <t>37037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66071</t>
+          <t>66006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>458347</t>
+          <t>458653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479317</t>
+          <t>479278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429256</t>
+          <t>429209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449118</t>
+          <t>449114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>894620</t>
+          <t>894685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924317</t>
+          <t>923654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183874</t>
+          <t>185696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234418</t>
+          <t>236013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129292</t>
+          <t>128428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171694</t>
+          <t>170850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325092</t>
+          <t>326642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390878</t>
+          <t>390987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>501071</t>
+          <t>499476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>551615</t>
+          <t>549793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451125</t>
+          <t>451969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493527</t>
+          <t>494391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>967429</t>
+          <t>967320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1033215</t>
+          <t>1031665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165536</t>
+          <t>166635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210408</t>
+          <t>213687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86476</t>
+          <t>85847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126361</t>
+          <t>123047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>265083</t>
+          <t>265823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>327220</t>
+          <t>326463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427378</t>
+          <t>424099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472250</t>
+          <t>471151</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>563383</t>
+          <t>566697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>603268</t>
+          <t>603897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1000310</t>
+          <t>1001067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1062447</t>
+          <t>1061707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90314</t>
+          <t>90693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130639</t>
+          <t>129673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125146</t>
+          <t>122195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170706</t>
+          <t>169635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>388508</t>
+          <t>389474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>428833</t>
+          <t>428454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>465229</t>
+          <t>462916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>490450</t>
+          <t>487841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>864083</t>
+          <t>865154</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>909643</t>
+          <t>912594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66545</t>
+          <t>67888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44664</t>
+          <t>43940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>68072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103303</t>
+          <t>103762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>320165</t>
+          <t>318822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346520</t>
+          <t>346244</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>358307</t>
+          <t>359031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379638</t>
+          <t>379872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>686378</t>
+          <t>685919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>722507</t>
+          <t>721609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55107</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84230</t>
+          <t>87021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93196</t>
+          <t>92832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129946</t>
+          <t>130208</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208353</t>
+          <t>205562</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>235339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290235</t>
+          <t>290352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312605</t>
+          <t>313834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>505571</t>
+          <t>505309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542321</t>
+          <t>542685</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24785</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45190</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63320</t>
+          <t>62330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164693</t>
+          <t>163309</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>185098</t>
+          <t>185444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309474</t>
+          <t>309736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324917</t>
+          <t>325803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480471</t>
+          <t>481461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>507511</t>
+          <t>508405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>640571</t>
+          <t>639436</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>736856</t>
+          <t>734655</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371045</t>
+          <t>367576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>445792</t>
+          <t>444153</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1029471</t>
+          <t>1027807</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1154499</t>
+          <t>1148678</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2538805</t>
+          <t>2541006</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2635090</t>
+          <t>2636225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2928853</t>
+          <t>2930492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3003600</t>
+          <t>3007069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5495808</t>
+          <t>5501629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5620836</t>
+          <t>5622500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20527</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>47039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49379</t>
+          <t>49010</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79702</t>
+          <t>79420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412186</t>
+          <t>414037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433619</t>
+          <t>434599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383938</t>
+          <t>383191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405590</t>
+          <t>405929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804674</t>
+          <t>804956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834997</t>
+          <t>835366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173550</t>
+          <t>171229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220864</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139703</t>
+          <t>144994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182845</t>
+          <t>191059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323846</t>
+          <t>324546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390362</t>
+          <t>388507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466223</t>
+          <t>467697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>513537</t>
+          <t>515858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427410</t>
+          <t>419196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470552</t>
+          <t>465261</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906980</t>
+          <t>908835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973496</t>
+          <t>972796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271801</t>
+          <t>267425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>321860</t>
+          <t>322675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130237</t>
+          <t>131171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175746</t>
+          <t>176715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415121</t>
+          <t>414304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>488272</t>
+          <t>484178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>360003</t>
+          <t>359188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410062</t>
+          <t>414438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534102</t>
+          <t>533133</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579611</t>
+          <t>578677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>903439</t>
+          <t>907533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>976590</t>
+          <t>977407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181598</t>
+          <t>179519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232826</t>
+          <t>228910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97154</t>
+          <t>99759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251905</t>
+          <t>250006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313737</t>
+          <t>314792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381791</t>
+          <t>385707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433019</t>
+          <t>435098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>519045</t>
+          <t>516440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>554347</t>
+          <t>552536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>917079</t>
+          <t>916024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>978911</t>
+          <t>980810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92861</t>
+          <t>95093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>132623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65860</t>
+          <t>67583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139894</t>
+          <t>141330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185440</t>
+          <t>191542</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296096</t>
+          <t>295747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335509</t>
+          <t>333277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381940</t>
+          <t>380217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410590</t>
+          <t>409948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>690730</t>
+          <t>684628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736276</t>
+          <t>734840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54738</t>
+          <t>56038</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84262</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82008</t>
+          <t>81548</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118155</t>
+          <t>119842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225524</t>
+          <t>224444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255048</t>
+          <t>253748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>310994</t>
+          <t>310154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>332831</t>
+          <t>332519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544628</t>
+          <t>542941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>580775</t>
+          <t>581235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45597</t>
+          <t>46008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>31076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71139</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204254</t>
+          <t>203843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227126</t>
+          <t>226711</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>358497</t>
+          <t>357903</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376778</t>
+          <t>376811</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>567691</t>
+          <t>570979</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598472</t>
+          <t>599007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>885148</t>
+          <t>883601</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>996643</t>
+          <t>998295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>487569</t>
+          <t>489634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>570891</t>
+          <t>579077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1400238</t>
+          <t>1403293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1548024</t>
+          <t>1543968</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2429076</t>
+          <t>2427424</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2540571</t>
+          <t>2542118</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2985417</t>
+          <t>2977231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3068739</t>
+          <t>3066674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5434003</t>
+          <t>5438059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5581789</t>
+          <t>5578734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>31235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57382</t>
+          <t>55500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>48993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81126</t>
+          <t>79144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388004</t>
+          <t>387499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404400</t>
+          <t>404881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338373</t>
+          <t>340255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>364417</t>
+          <t>364520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732257</t>
+          <t>734239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>763291</t>
+          <t>764390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196601</t>
+          <t>196271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243568</t>
+          <t>244604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127717</t>
+          <t>128386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168887</t>
+          <t>168814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>336065</t>
+          <t>336058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399993</t>
+          <t>402117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346928</t>
+          <t>345892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393895</t>
+          <t>394225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393722</t>
+          <t>393795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>434892</t>
+          <t>434223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>753113</t>
+          <t>750989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>817041</t>
+          <t>817048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285381</t>
+          <t>284859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>336624</t>
+          <t>338581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>196076</t>
+          <t>196028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244327</t>
+          <t>243611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>497066</t>
+          <t>493090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566384</t>
+          <t>567544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>329771</t>
+          <t>327814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381014</t>
+          <t>381536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416130</t>
+          <t>416846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>464381</t>
+          <t>464429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>760468</t>
+          <t>759308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829786</t>
+          <t>833762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219486</t>
+          <t>220404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>271523</t>
+          <t>270233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107307</t>
+          <t>107334</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147825</t>
+          <t>148013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>335982</t>
+          <t>335242</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404439</t>
+          <t>403864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371808</t>
+          <t>373098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>423845</t>
+          <t>422927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>500211</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>540729</t>
+          <t>540702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886928</t>
+          <t>887503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>955385</t>
+          <t>956125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139969</t>
+          <t>139655</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184206</t>
+          <t>183699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50676</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>82336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199777</t>
+          <t>200785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252199</t>
+          <t>256511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>293712</t>
+          <t>294219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337949</t>
+          <t>338263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>412181</t>
+          <t>413410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445070</t>
+          <t>445922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>721465</t>
+          <t>717153</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>773887</t>
+          <t>772879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75975</t>
+          <t>76940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>111223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113058</t>
+          <t>112156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153560</t>
+          <t>152581</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224661</t>
+          <t>222057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257305</t>
+          <t>256340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326193</t>
+          <t>325961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349064</t>
+          <t>349884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>556527</t>
+          <t>557506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597029</t>
+          <t>597931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36609</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>48151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79404</t>
+          <t>80226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197180</t>
+          <t>197963</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219653</t>
+          <t>219715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371235</t>
+          <t>371418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391586</t>
+          <t>391598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>577027</t>
+          <t>576205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>607433</t>
+          <t>608280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1039782</t>
+          <t>1046073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1155736</t>
+          <t>1157803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>610279</t>
+          <t>608342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>703337</t>
+          <t>703798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1676119</t>
+          <t>1681725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1828966</t>
+          <t>1826660</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2229573</t>
+          <t>2227506</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2345527</t>
+          <t>2339236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2836243</t>
+          <t>2835782</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2929301</t>
+          <t>2931238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5095924</t>
+          <t>5098230</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5248771</t>
+          <t>5243165</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -9665,27 +9665,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39606</t>
+          <t>41907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>36350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72548</t>
+          <t>75447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -9778,22 +9778,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374407</t>
+          <t>381875</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352493</t>
+          <t>359401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386925</t>
+          <t>394745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>287608</t>
+          <t>336391</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273594</t>
+          <t>320605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297523</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>662015</t>
+          <t>718266</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640639</t>
+          <t>694858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>678644</t>
+          <t>733955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>122108</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101214</t>
+          <t>105797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147199</t>
+          <t>158123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114006</t>
+          <t>123143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>104480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141984</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>236114</t>
+          <t>252738</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176405</t>
+          <t>219563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271058</t>
+          <t>285318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>301439</t>
+          <t>347295</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276348</t>
+          <t>318767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322333</t>
+          <t>371093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>398087</t>
+          <t>378590</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370109</t>
+          <t>358220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445100</t>
+          <t>397253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>699526</t>
+          <t>725885</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664582</t>
+          <t>693305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>759235</t>
+          <t>759060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>236897</t>
+          <t>268035</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211348</t>
+          <t>241807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260161</t>
+          <t>294271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>204035</t>
+          <t>224145</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154829</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230184</t>
+          <t>245961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>440932</t>
+          <t>492180</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384427</t>
+          <t>458005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>478198</t>
+          <t>523231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>299441</t>
+          <t>352802</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276177</t>
+          <t>326566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324990</t>
+          <t>379030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>387967</t>
+          <t>399048</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361818</t>
+          <t>377232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437173</t>
+          <t>419417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>687408</t>
+          <t>751849</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650142</t>
+          <t>720798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743913</t>
+          <t>786024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>214530</t>
+          <t>238732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93812</t>
+          <t>213594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>308998</t>
+          <t>266977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>201669</t>
+          <t>214195</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171442</t>
+          <t>196583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225337</t>
+          <t>235093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>416198</t>
+          <t>452927</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256934</t>
+          <t>421416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>508589</t>
+          <t>487109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>673256</t>
+          <t>461885</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>578788</t>
+          <t>433640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>793974</t>
+          <t>487023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>510518</t>
+          <t>522015</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>486850</t>
+          <t>501117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>540745</t>
+          <t>539627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1183775</t>
+          <t>983900</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1091384</t>
+          <t>949718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1343039</t>
+          <t>1015411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712187</t>
+          <t>736210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599973</t>
+          <t>1436827</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>177074</t>
+          <t>192479</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156183</t>
+          <t>170615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>201514</t>
+          <t>213134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>113932</t>
+          <t>127506</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99637</t>
+          <t>112383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128405</t>
+          <t>144684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>291006</t>
+          <t>319985</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>265628</t>
+          <t>294013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313863</t>
+          <t>348054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>384160</t>
+          <t>416867</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359720</t>
+          <t>396212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>405051</t>
+          <t>438731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>433973</t>
+          <t>481349</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419500</t>
+          <t>464171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>448268</t>
+          <t>496472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>818133</t>
+          <t>898217</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>795276</t>
+          <t>870148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>843511</t>
+          <t>924189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>100159</t>
+          <t>110847</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87153</t>
+          <t>96671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115080</t>
+          <t>128012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>56377</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>46816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83387</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>152438</t>
+          <t>167223</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>149938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200516</t>
+          <t>185793</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>295139</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251986</t>
+          <t>277974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279913</t>
+          <t>309315</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>555523</t>
+          <t>382221</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>524415</t>
+          <t>371541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588511</t>
+          <t>391782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>822431</t>
+          <t>677361</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>774353</t>
+          <t>658791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>898972</t>
+          <t>694646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>844584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>55883</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67310</t>
+          <t>72174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>79698</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67680</t>
+          <t>72117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92805</t>
+          <t>100484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>226876</t>
+          <t>250543</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215449</t>
+          <t>238024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236741</t>
+          <t>262258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>402015</t>
+          <t>439076</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>395026</t>
+          <t>431451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>407809</t>
+          <t>445379</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>628892</t>
+          <t>689619</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>615785</t>
+          <t>674323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640910</t>
+          <t>702690</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>932230</t>
+          <t>1025259</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>734467</t>
+          <t>964591</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1027734</t>
+          <t>1085978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>735328</t>
+          <t>797020</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>592589</t>
+          <t>750751</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>809525</t>
+          <t>837236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1667558</t>
+          <t>1822280</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1453819</t>
+          <t>1744970</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1803776</t>
+          <t>1897108</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2526488</t>
+          <t>2506410</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2430984</t>
+          <t>2445691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2724251</t>
+          <t>2567078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2975692</t>
+          <t>2938689</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2901495</t>
+          <t>2898473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3118431</t>
+          <t>2984958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5502180</t>
+          <t>5445098</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5365962</t>
+          <t>5370270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5715919</t>
+          <t>5522408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
